--- a/output/graficos_regionales/plot_regional_serie_i_ingr_m_2023_metropolitana.xlsx
+++ b/output/graficos_regionales/plot_regional_serie_i_ingr_m_2023_metropolitana.xlsx
@@ -288,7 +288,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-28 16:40</t>
+    <t xml:space="preserve">2026-10-05 02:00</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -712,7 +712,7 @@
         <v>4</v>
       </c>
       <c r="B3" s="2" t="n">
-        <v>885628.12</v>
+        <v>885628.13</v>
       </c>
       <c r="C3" s="2" t="n">
         <v>781160</v>
@@ -726,7 +726,7 @@
         <v>904589.44</v>
       </c>
       <c r="C4" s="2" t="n">
-        <v>804762.62</v>
+        <v>804762.63</v>
       </c>
     </row>
     <row r="5">
@@ -737,7 +737,7 @@
         <v>894332.81</v>
       </c>
       <c r="C5" s="2" t="n">
-        <v>799364.12</v>
+        <v>799364.13</v>
       </c>
     </row>
     <row r="6">
@@ -756,7 +756,7 @@
         <v>8</v>
       </c>
       <c r="B7" s="2" t="n">
-        <v>896373.12</v>
+        <v>896373.13</v>
       </c>
       <c r="C7" s="2" t="n">
         <v>802344.94</v>
@@ -767,7 +767,7 @@
         <v>9</v>
       </c>
       <c r="B8" s="2" t="n">
-        <v>899575.62</v>
+        <v>899575.63</v>
       </c>
       <c r="C8" s="2" t="n">
         <v>805474.38</v>
@@ -836,7 +836,7 @@
         <v>932712.75</v>
       </c>
       <c r="C14" s="2" t="n">
-        <v>826816.62</v>
+        <v>826816.63</v>
       </c>
     </row>
     <row r="15">
@@ -844,7 +844,7 @@
         <v>16</v>
       </c>
       <c r="B15" s="2" t="n">
-        <v>923225.12</v>
+        <v>923225.13</v>
       </c>
       <c r="C15" s="2" t="n">
         <v>816360.81</v>
@@ -910,10 +910,10 @@
         <v>22</v>
       </c>
       <c r="B21" s="2" t="n">
-        <v>948825.62</v>
+        <v>948825.63</v>
       </c>
       <c r="C21" s="2" t="n">
-        <v>849932.62</v>
+        <v>849932.63</v>
       </c>
     </row>
     <row r="22">
@@ -943,7 +943,7 @@
         <v>25</v>
       </c>
       <c r="B24" s="2" t="n">
-        <v>963047.62</v>
+        <v>963047.63</v>
       </c>
       <c r="C24" s="2" t="n">
         <v>864071.75</v>
@@ -1001,7 +1001,7 @@
         <v>981252</v>
       </c>
       <c r="C29" s="2" t="n">
-        <v>885489.12</v>
+        <v>885489.13</v>
       </c>
     </row>
     <row r="30">
@@ -1012,7 +1012,7 @@
         <v>959046.88</v>
       </c>
       <c r="C30" s="2" t="n">
-        <v>873830.12</v>
+        <v>873830.13</v>
       </c>
     </row>
     <row r="31">
@@ -1086,7 +1086,7 @@
         <v>38</v>
       </c>
       <c r="B37" s="2" t="n">
-        <v>1083734.12</v>
+        <v>1083734.13</v>
       </c>
       <c r="C37" s="2" t="n">
         <v>969716.44</v>
@@ -1166,7 +1166,7 @@
         <v>1038779.69</v>
       </c>
       <c r="C44" s="2" t="n">
-        <v>953641.12</v>
+        <v>953641.13</v>
       </c>
     </row>
     <row r="45">
@@ -1218,7 +1218,7 @@
         <v>50</v>
       </c>
       <c r="B49" s="2" t="n">
-        <v>1155870.62</v>
+        <v>1155870.63</v>
       </c>
       <c r="C49" s="2" t="n">
         <v>1049309.75</v>
@@ -1229,7 +1229,7 @@
         <v>51</v>
       </c>
       <c r="B50" s="2" t="n">
-        <v>1103470.12</v>
+        <v>1103470.13</v>
       </c>
       <c r="C50" s="2" t="n">
         <v>990892.69</v>
@@ -1287,7 +1287,7 @@
         <v>1157608.5</v>
       </c>
       <c r="C55" s="2" t="n">
-        <v>1048559.62</v>
+        <v>1048559.63</v>
       </c>
     </row>
     <row r="56">
@@ -1298,7 +1298,7 @@
         <v>1169431</v>
       </c>
       <c r="C56" s="2" t="n">
-        <v>1059287.62</v>
+        <v>1059287.63</v>
       </c>
     </row>
     <row r="57">
@@ -1306,7 +1306,7 @@
         <v>58</v>
       </c>
       <c r="B57" s="2" t="n">
-        <v>1188130.12</v>
+        <v>1188130.13</v>
       </c>
       <c r="C57" s="2" t="n">
         <v>1074313.38</v>
@@ -1339,10 +1339,10 @@
         <v>61</v>
       </c>
       <c r="B60" s="2" t="n">
-        <v>1210918.12</v>
+        <v>1210918.13</v>
       </c>
       <c r="C60" s="2" t="n">
-        <v>1093564.62</v>
+        <v>1093564.63</v>
       </c>
     </row>
     <row r="61">
@@ -1350,7 +1350,7 @@
         <v>62</v>
       </c>
       <c r="B61" s="2" t="n">
-        <v>1310677.62</v>
+        <v>1310677.63</v>
       </c>
       <c r="C61" s="2" t="n">
         <v>1183065.88</v>
@@ -1361,10 +1361,10 @@
         <v>63</v>
       </c>
       <c r="B62" s="2" t="n">
-        <v>1266345.62</v>
+        <v>1266345.63</v>
       </c>
       <c r="C62" s="2" t="n">
-        <v>1145616.62</v>
+        <v>1145616.63</v>
       </c>
     </row>
     <row r="63">
@@ -1383,7 +1383,7 @@
         <v>65</v>
       </c>
       <c r="B64" s="2" t="n">
-        <v>1280429.12</v>
+        <v>1280429.13</v>
       </c>
       <c r="C64" s="2" t="n">
         <v>1158414.88</v>
@@ -1419,7 +1419,7 @@
         <v>1301183</v>
       </c>
       <c r="C67" s="2" t="n">
-        <v>1184430.62</v>
+        <v>1184430.63</v>
       </c>
     </row>
     <row r="68">
@@ -1427,7 +1427,7 @@
         <v>69</v>
       </c>
       <c r="B68" s="2" t="n">
-        <v>1304572.12</v>
+        <v>1304572.13</v>
       </c>
       <c r="C68" s="2" t="n">
         <v>1185328.75</v>
@@ -1438,7 +1438,7 @@
         <v>70</v>
       </c>
       <c r="B69" s="2" t="n">
-        <v>1304973.12</v>
+        <v>1304973.13</v>
       </c>
       <c r="C69" s="2" t="n">
         <v>1186515.5</v>
@@ -1460,7 +1460,7 @@
         <v>72</v>
       </c>
       <c r="B71" s="2" t="n">
-        <v>1324207.62</v>
+        <v>1324207.63</v>
       </c>
       <c r="C71" s="2" t="n">
         <v>1202545</v>
@@ -1482,7 +1482,7 @@
         <v>74</v>
       </c>
       <c r="B73" s="2" t="n">
-        <v>1424862.12</v>
+        <v>1424862.13</v>
       </c>
       <c r="C73" s="2" t="n">
         <v>1284570.75</v>
@@ -1504,7 +1504,7 @@
         <v>76</v>
       </c>
       <c r="B75" s="2" t="n">
-        <v>1354749.62</v>
+        <v>1354749.63</v>
       </c>
       <c r="C75" s="2" t="n">
         <v>1214165.25</v>
@@ -1518,7 +1518,7 @@
         <v>1379808.5</v>
       </c>
       <c r="C76" s="2" t="n">
-        <v>1240434.12</v>
+        <v>1240434.13</v>
       </c>
     </row>
     <row r="77">
@@ -1548,10 +1548,10 @@
         <v>80</v>
       </c>
       <c r="B79" s="2" t="n">
-        <v>1384566.12</v>
+        <v>1384566.13</v>
       </c>
       <c r="C79" s="2" t="n">
-        <v>1253268.12</v>
+        <v>1253268.13</v>
       </c>
     </row>
     <row r="80">
@@ -1562,7 +1562,7 @@
         <v>1407172.38</v>
       </c>
       <c r="C80" s="2" t="n">
-        <v>1274861.62</v>
+        <v>1274861.63</v>
       </c>
     </row>
     <row r="81">
@@ -1570,7 +1570,7 @@
         <v>82</v>
       </c>
       <c r="B81" s="2" t="n">
-        <v>1405816.12</v>
+        <v>1405816.13</v>
       </c>
       <c r="C81" s="2" t="n">
         <v>1271870.5</v>
@@ -1581,10 +1581,10 @@
         <v>83</v>
       </c>
       <c r="B82" s="2" t="n">
-        <v>1461769.12</v>
+        <v>1461769.13</v>
       </c>
       <c r="C82" s="2" t="n">
-        <v>1327655.12</v>
+        <v>1327655.13</v>
       </c>
     </row>
     <row r="83">
